--- a/docs/samples/image-mapping-template.xlsx
+++ b/docs/samples/image-mapping-template.xlsx
@@ -22,19 +22,19 @@
     <t>position</t>
   </si>
   <si>
-    <t>dk-tshirt-001_1.jpg</t>
-  </si>
-  <si>
-    <t>DK-TSHIRT-001</t>
-  </si>
-  <si>
-    <t>dk-tshirt-001_2.jpg</t>
+    <t>dg-tshirt-001_1.jpg</t>
+  </si>
+  <si>
+    <t>DG-TSHIRT-001</t>
+  </si>
+  <si>
+    <t>dg-tshirt-001_2.jpg</t>
   </si>
   <si>
     <t>earbuds-front.png</t>
   </si>
   <si>
-    <t>DK-EARBUD-002</t>
+    <t>DG-EARBUD-002</t>
   </si>
 </sst>
 </file>
